--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484669_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484669_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. CAMPOS DE BENGOA</t>
+          <t>P. MORTE MONTANES</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,58 +565,58 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.4122</v>
+        <v>5.2109</v>
       </c>
       <c r="E2" t="n">
-        <v>2.7272</v>
+        <v>3.1427</v>
       </c>
       <c r="F2" t="n">
-        <v>3.685</v>
+        <v>2.0682</v>
       </c>
       <c r="G2" t="n">
-        <v>3.5142</v>
+        <v>3.453</v>
       </c>
       <c r="H2" t="n">
-        <v>2.2159</v>
+        <v>0.8854</v>
       </c>
       <c r="I2" t="n">
-        <v>1.2983</v>
+        <v>2.5676</v>
       </c>
       <c r="J2" t="n">
-        <v>2.2905</v>
+        <v>3.4474</v>
       </c>
       <c r="K2" t="n">
-        <v>1.5047</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7857</v>
+        <v>2.7603</v>
       </c>
       <c r="M2" t="n">
-        <v>1.2237</v>
+        <v>0.0056</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7112000000000001</v>
+        <v>0.1983</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5125</v>
+        <v>-0.1928</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1833</v>
+        <v>1.0995</v>
       </c>
       <c r="Q2" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R2" t="n">
-        <v>1.0995</v>
+        <v>2.0158</v>
       </c>
       <c r="S2" t="n">
-        <v>3.0367</v>
+        <v>0.9804</v>
       </c>
       <c r="T2" t="n">
-        <v>1.353</v>
+        <v>0.6116</v>
       </c>
       <c r="U2" t="n">
-        <v>1.6837</v>
+        <v>0.3688</v>
       </c>
       <c r="V2" t="n">
         <v>-0.3219</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. MORTE MONTANES</t>
+          <t>J. CAMPOS DE BENGOA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,58 +643,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.6888</v>
+        <v>5.1396</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7197</v>
+        <v>1.8757</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9691</v>
+        <v>3.2639</v>
       </c>
       <c r="G3" t="n">
-        <v>3.453</v>
+        <v>3.5142</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8854</v>
+        <v>2.2159</v>
       </c>
       <c r="I3" t="n">
-        <v>2.5676</v>
+        <v>1.2983</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4474</v>
+        <v>2.2905</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6870000000000001</v>
+        <v>1.5047</v>
       </c>
       <c r="L3" t="n">
-        <v>2.7603</v>
+        <v>0.7857</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0056</v>
+        <v>1.2237</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1983</v>
+        <v>0.7112000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1928</v>
+        <v>0.5125</v>
       </c>
       <c r="P3" t="n">
-        <v>1.0995</v>
+        <v>0.1833</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0158</v>
+        <v>1.0995</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4582</v>
+        <v>1.7641</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1886</v>
+        <v>0.5014999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2697</v>
+        <v>1.2626</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3219</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. MORAGAS AZNAR</t>
+          <t>D. GARCIA ROYO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.8009</v>
+        <v>3.775</v>
       </c>
       <c r="E4" t="n">
-        <v>3.8165</v>
+        <v>2.0522</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0156</v>
+        <v>1.7229</v>
       </c>
       <c r="G4" t="n">
-        <v>5.8671</v>
+        <v>1.6907</v>
       </c>
       <c r="H4" t="n">
-        <v>4.2224</v>
+        <v>3.5116</v>
       </c>
       <c r="I4" t="n">
-        <v>1.6447</v>
+        <v>-1.8209</v>
       </c>
       <c r="J4" t="n">
-        <v>5.3746</v>
+        <v>1.8041</v>
       </c>
       <c r="K4" t="n">
-        <v>3.9539</v>
+        <v>2.9195</v>
       </c>
       <c r="L4" t="n">
-        <v>1.4207</v>
+        <v>-1.1154</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4925</v>
+        <v>-0.1134</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2685</v>
+        <v>0.5921999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>0.224</v>
+        <v>-0.7056</v>
       </c>
       <c r="P4" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="Q4" t="n">
         <v>-0.9163</v>
       </c>
-      <c r="Q4" t="n">
-        <v>-2.7489</v>
-      </c>
       <c r="R4" t="n">
-        <v>1.8326</v>
+        <v>1.6493</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7401</v>
+        <v>1.0398</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5468</v>
+        <v>0.2089</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1933</v>
+        <v>0.8309</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.89</v>
+        <v>0.3115</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6439</v>
+        <v>0.9554</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.5339</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. GARCIA ROYO</t>
+          <t>M. MORAGAS AZNAR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.4038</v>
+        <v>3.5788</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8048</v>
+        <v>3.4458</v>
       </c>
       <c r="F5" t="n">
-        <v>1.599</v>
+        <v>0.1331</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6907</v>
+        <v>5.8671</v>
       </c>
       <c r="H5" t="n">
-        <v>3.5116</v>
+        <v>4.2224</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.8209</v>
+        <v>1.6447</v>
       </c>
       <c r="J5" t="n">
-        <v>1.8041</v>
+        <v>5.3746</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9195</v>
+        <v>3.9539</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.1154</v>
+        <v>1.4207</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1134</v>
+        <v>0.4925</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5921999999999999</v>
+        <v>0.2685</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7056</v>
+        <v>0.224</v>
       </c>
       <c r="P5" t="n">
-        <v>0.733</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9163</v>
+        <v>-2.7489</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6493</v>
+        <v>1.8326</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6686</v>
+        <v>0.5181</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0384</v>
+        <v>0.1761</v>
       </c>
       <c r="U5" t="n">
-        <v>0.707</v>
+        <v>0.342</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3115</v>
+        <v>-1.89</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9554</v>
+        <v>0.6439</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6439</v>
+        <v>-2.5339</v>
       </c>
     </row>
     <row r="6">
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. MORTE MONTAÑES</t>
+          <t>J. SABATE PRATS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2753</v>
+        <v>1.5648</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2753</v>
+        <v>0.9478</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>0.617</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2753</v>
+        <v>-1.0926</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6502</v>
+        <v>0.2057</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6251</v>
+        <v>-1.2983</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2753</v>
+        <v>0.0557</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6502</v>
+        <v>0.5202</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6251</v>
+        <v>-0.4645</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-1.1483</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-0.3145</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-0.8338</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.2828</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>0.9847</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.5023</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.4824</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>2.2224</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.2224</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>V. RODRIGUEZ GIL</t>
+          <t>P. MORTE MONTAÑES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7949000000000001</v>
+        <v>1.2753</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9996</v>
+        <v>1.2753</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2047</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.0578</v>
+        <v>1.2753</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0963</v>
+        <v>0.6502</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.1541</v>
+        <v>0.6251</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1301</v>
+        <v>1.2753</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.0624</v>
+        <v>0.6502</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1925</v>
+        <v>0.6251</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1879</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1587</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.3466</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5498</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4661</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.9364</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1.4638</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4726</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6335</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.9554</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. SABATE PRATS</t>
+          <t>V. RODRIGUEZ GIL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5234</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0688</v>
+        <v>0.4777</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5921999999999999</v>
+        <v>-0.3781</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.0926</v>
+        <v>-1.0578</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2057</v>
+        <v>0.0963</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.2983</v>
+        <v>-1.1541</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0557</v>
+        <v>0.1301</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5202</v>
+        <v>-0.0624</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.4645</v>
+        <v>0.1925</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.1483</v>
+        <v>-1.1879</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3145</v>
+        <v>0.1587</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8338</v>
+        <v>-1.3466</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.5498</v>
+        <v>0.5498</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2828</v>
+        <v>1.4661</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0566</v>
+        <v>1.2411</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5143</v>
+        <v>0.9419</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4577</v>
+        <v>0.2992</v>
       </c>
       <c r="V9" t="n">
-        <v>2.2224</v>
+        <v>-0.6335</v>
       </c>
       <c r="W9" t="n">
-        <v>2.2224</v>
+        <v>0.3219</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1138</v>
+        <v>0.0584</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4914</v>
+        <v>-0.2991</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6052999999999999</v>
+        <v>0.3575</v>
       </c>
       <c r="G10" t="n">
         <v>-1.1879</v>
@@ -1234,13 +1234,13 @@
         <v>0.9163</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2376</v>
+        <v>-0.293</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7157</v>
+        <v>-0.5234</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4781</v>
+        <v>0.2304</v>
       </c>
       <c r="V10" t="n">
         <v>0.6231</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7458</v>
+        <v>-0.9097</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.486</v>
+        <v>-2.0464</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7402</v>
+        <v>1.1366</v>
       </c>
       <c r="G11" t="n">
         <v>-2.0487</v>
@@ -1312,13 +1312,13 @@
         <v>1.6493</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4039</v>
+        <v>-0.5679</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.101</v>
+        <v>-0.6614</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3029</v>
+        <v>0.0935</v>
       </c>
       <c r="V11" t="n">
         <v>1.89</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. PEREZ RIPOLL</t>
+          <t>J. VILLAR SOLER</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.3209</v>
+        <v>-1.995</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.8703</v>
+        <v>-2.0895</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4506</v>
+        <v>0.0945</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.7717</v>
+        <v>-3.5114</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1517</v>
+        <v>-0.6973</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.9234</v>
+        <v>-2.8142</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.6968</v>
+        <v>-2.2992</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.0558</v>
+        <v>-0.511</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.641</v>
+        <v>-1.7882</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.0748</v>
+        <v>-1.2122</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2075</v>
+        <v>-0.1863</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.2824</v>
+        <v>-1.0259</v>
       </c>
       <c r="P12" t="n">
-        <v>0.5498</v>
+        <v>0.733</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4661</v>
+        <v>0.733</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7771</v>
+        <v>0.7834</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2572</v>
+        <v>0.2097</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5199</v>
+        <v>0.5737</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. VILLAR SOLER</t>
+          <t>A. PEREZ RIPOLL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.6077</v>
+        <v>-2.0295</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.7766</v>
+        <v>-1.678</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1688</v>
+        <v>-0.3515</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.5114</v>
+        <v>-1.7717</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.6973</v>
+        <v>0.1517</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.8142</v>
+        <v>-1.9234</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.2992</v>
+        <v>-0.6968</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.511</v>
+        <v>-0.0558</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.7882</v>
+        <v>-0.641</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.2122</v>
+        <v>-1.0748</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1863</v>
+        <v>0.2075</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.0259</v>
+        <v>-1.2824</v>
       </c>
       <c r="P13" t="n">
-        <v>0.733</v>
+        <v>0.5498</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R13" t="n">
-        <v>0.733</v>
+        <v>1.4661</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1707</v>
+        <v>-0.4857</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4774</v>
+        <v>-0.0648</v>
       </c>
       <c r="U13" t="n">
-        <v>0.648</v>
+        <v>-0.4208</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.6085</v>
+        <v>-3.4876</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.3682</v>
+        <v>-1.2721</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.2403</v>
+        <v>-2.2155</v>
       </c>
       <c r="G14" t="n">
         <v>-1.981</v>
@@ -1546,13 +1546,13 @@
         <v>0.5498</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5883</v>
+        <v>-0.4674</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5505</v>
+        <v>-0.4544</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0378</v>
+        <v>-0.013</v>
       </c>
       <c r="V14" t="n">
         <v>-1.5889</v>
@@ -1579,16 +1579,16 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>13.6558</v>
+        <v>14.2062</v>
       </c>
       <c r="E15" t="n">
-        <v>7.207399999999998</v>
+        <v>7.757700000000002</v>
       </c>
       <c r="F15" t="n">
-        <v>6.448399999999999</v>
+        <v>6.448600000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>5.0748</v>
+        <v>5.074799999999999</v>
       </c>
       <c r="H15" t="n">
         <v>13.8899</v>
@@ -1624,13 +1624,13 @@
         <v>14.6606</v>
       </c>
       <c r="S15" t="n">
-        <v>4.9472</v>
+        <v>5.4976</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8976999999999997</v>
+        <v>1.448</v>
       </c>
       <c r="U15" t="n">
-        <v>4.0495</v>
+        <v>4.049700000000001</v>
       </c>
       <c r="V15" t="n">
         <v>-0.03110000000000035</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.772</v>
+        <v>2.8959</v>
       </c>
       <c r="E16" t="n">
         <v>2.5154</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2566</v>
+        <v>0.3805</v>
       </c>
       <c r="G16" t="n">
         <v>2.6163</v>
@@ -1702,13 +1702,13 @@
         <v>0.1833</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0275</v>
+        <v>0.0963</v>
       </c>
       <c r="T16" t="n">
         <v>-0.1101</v>
       </c>
       <c r="U16" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.2064</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.5471</v>
+        <v>2.5718</v>
       </c>
       <c r="E17" t="n">
         <v>2.7993</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2523</v>
+        <v>-0.2275</v>
       </c>
       <c r="G17" t="n">
         <v>2.3368</v>
@@ -1780,13 +1780,13 @@
         <v>1.0995</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2949</v>
+        <v>-0.2702</v>
       </c>
       <c r="T17" t="n">
         <v>-0.0196</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2754</v>
+        <v>-0.2506</v>
       </c>
       <c r="V17" t="n">
         <v>0.3219</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. MATEO LAZARO</t>
+          <t>G. LOPEZ ABAD</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3507</v>
+        <v>-0.299</v>
       </c>
       <c r="E21" t="n">
-        <v>1.8484</v>
+        <v>-0.9356</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4976</v>
+        <v>0.6366000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.2199</v>
+        <v>0.2397</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.1942</v>
+        <v>-1.1833</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.0256</v>
+        <v>1.423</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.258</v>
+        <v>1.0385</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.7776</v>
+        <v>0.0959</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.4804</v>
+        <v>0.9426</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.9618</v>
+        <v>-0.7988</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.4166</v>
+        <v>-1.2792</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5452</v>
+        <v>0.4804</v>
       </c>
       <c r="P21" t="n">
-        <v>1.2828</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2828</v>
+        <v>1.4661</v>
       </c>
       <c r="S21" t="n">
-        <v>1.0312</v>
+        <v>-0.4942</v>
       </c>
       <c r="T21" t="n">
-        <v>1.2059</v>
+        <v>-0.7854</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1747</v>
+        <v>0.2913</v>
       </c>
       <c r="V21" t="n">
-        <v>1.2566</v>
+        <v>0.3219</v>
       </c>
       <c r="W21" t="n">
-        <v>1.9005</v>
+        <v>0.6439</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.6439</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>G. LOPEZ ABAD</t>
+          <t>J. MATEO LAZARO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.516</v>
+        <v>-0.4067</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4164</v>
+        <v>0.6945</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9004</v>
+        <v>-1.1012</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2397</v>
+        <v>-3.2199</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.1833</v>
+        <v>-2.1942</v>
       </c>
       <c r="I22" t="n">
-        <v>1.423</v>
+        <v>-1.0256</v>
       </c>
       <c r="J22" t="n">
-        <v>1.0385</v>
+        <v>-1.258</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0959</v>
+        <v>-0.7776</v>
       </c>
       <c r="L22" t="n">
-        <v>0.9426</v>
+        <v>-0.4804</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.7988</v>
+        <v>-1.9618</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.2792</v>
+        <v>-1.4166</v>
       </c>
       <c r="O22" t="n">
-        <v>0.4804</v>
+        <v>-0.5452</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.3665</v>
+        <v>1.2828</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4661</v>
+        <v>1.2828</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7111</v>
+        <v>0.2738</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.2662</v>
+        <v>0.0521</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5551</v>
+        <v>0.2217</v>
       </c>
       <c r="V22" t="n">
-        <v>0.3219</v>
+        <v>1.2566</v>
       </c>
       <c r="W22" t="n">
-        <v>0.6439</v>
+        <v>1.9005</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.3219</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. ORTEGA IBANEZ</t>
+          <t>J. BERMEJO DORRONSORO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.1199</v>
+        <v>-0.9361</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.2459</v>
+        <v>-1.0137</v>
       </c>
       <c r="F23" t="n">
-        <v>1.126</v>
+        <v>0.0776</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.955</v>
+        <v>0.0136</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.9165</v>
+        <v>-1.8423</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.0385</v>
+        <v>1.8559</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5778</v>
+        <v>0.2016</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.155</v>
+        <v>-1.1737</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.4228</v>
+        <v>1.3753</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.3772</v>
+        <v>-0.1879</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.7615</v>
+        <v>-0.6686</v>
       </c>
       <c r="O23" t="n">
-        <v>0.3843</v>
+        <v>0.4807</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.1991</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.6651</v>
+        <v>-0.9163</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4661</v>
+        <v>0.733</v>
       </c>
       <c r="S23" t="n">
-        <v>1.7673</v>
+        <v>-0.4446</v>
       </c>
       <c r="T23" t="n">
-        <v>0.73</v>
+        <v>-0.299</v>
       </c>
       <c r="U23" t="n">
-        <v>1.0372</v>
+        <v>-0.1456</v>
       </c>
       <c r="V23" t="n">
-        <v>1.267</v>
+        <v>-0.3219</v>
       </c>
       <c r="W23" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. BERMEJO DORRONSORO</t>
+          <t>I. RUIPEREZ SANCHEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.5219</v>
+        <v>-0.9574</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.3022</v>
+        <v>-0.3466</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.2197</v>
+        <v>-0.6108</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0136</v>
+        <v>-0.6916</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.8423</v>
+        <v>-0.5026</v>
       </c>
       <c r="I24" t="n">
-        <v>1.8559</v>
+        <v>-0.189</v>
       </c>
       <c r="J24" t="n">
-        <v>0.2016</v>
+        <v>0.3148</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.1737</v>
+        <v>0.0867</v>
       </c>
       <c r="L24" t="n">
-        <v>1.3753</v>
+        <v>0.2281</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.1879</v>
+        <v>-1.0063</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.6686</v>
+        <v>-0.5893</v>
       </c>
       <c r="O24" t="n">
-        <v>0.4807</v>
+        <v>-0.417</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.1833</v>
+        <v>1.0995</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.733</v>
+        <v>1.0995</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0303</v>
+        <v>-1.3654</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5875</v>
+        <v>-0.6614</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4428</v>
+        <v>-0.704</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>I. RUIPEREZ SANCHEZ</t>
+          <t>A. ORTEGA IBANEZ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,64 +2359,64 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.9453</v>
+        <v>-2.3555</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.7312</v>
+        <v>-3.0152</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.214</v>
+        <v>0.6597</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.6916</v>
+        <v>-1.955</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.5026</v>
+        <v>-1.9165</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.189</v>
+        <v>-0.0385</v>
       </c>
       <c r="J25" t="n">
-        <v>0.3148</v>
+        <v>-0.5778</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0867</v>
+        <v>-0.155</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2281</v>
+        <v>-0.4228</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.0063</v>
+        <v>-1.3772</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.5893</v>
+        <v>-1.7615</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.417</v>
+        <v>0.3843</v>
       </c>
       <c r="P25" t="n">
-        <v>1.0995</v>
+        <v>-2.1991</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>-3.6651</v>
       </c>
       <c r="R25" t="n">
-        <v>1.0995</v>
+        <v>1.4661</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.3532</v>
+        <v>0.5317</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.046</v>
+        <v>-0.0392</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.3072</v>
+        <v>0.5709</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.806</v>
+        <v>-2.5146</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.2333</v>
+        <v>-3.0409</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4273</v>
+        <v>0.5264</v>
       </c>
       <c r="G26" t="n">
         <v>-1.9843</v>
@@ -2482,13 +2482,13 @@
         <v>0.9163</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.2273</v>
+        <v>0.0641</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.3673</v>
+        <v>-0.175</v>
       </c>
       <c r="U26" t="n">
-        <v>0.14</v>
+        <v>0.2391</v>
       </c>
       <c r="V26" t="n">
         <v>0.3219</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-4.1021</v>
+        <v>-3.5761</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.2975</v>
+        <v>-2.2014</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.8046</v>
+        <v>-1.3748</v>
       </c>
       <c r="G27" t="n">
         <v>0.5311</v>
@@ -2560,13 +2560,13 @@
         <v>0.3665</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.9839</v>
+        <v>-0.458</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.3303</v>
+        <v>-0.2342</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.6536</v>
+        <v>-0.2238</v>
       </c>
       <c r="V27" t="n">
         <v>-1.267</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-4.8727</v>
+        <v>-4.0305</v>
       </c>
       <c r="E28" t="n">
-        <v>-3.1468</v>
+        <v>-2.8583</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.7259</v>
+        <v>-1.1722</v>
       </c>
       <c r="G28" t="n">
         <v>-2.5072</v>
@@ -2638,13 +2638,13 @@
         <v>0.733</v>
       </c>
       <c r="S28" t="n">
-        <v>-2.203</v>
+        <v>-1.3609</v>
       </c>
       <c r="T28" t="n">
-        <v>-1.3212</v>
+        <v>-1.0328</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.8818</v>
+        <v>-0.3281</v>
       </c>
       <c r="V28" t="n">
         <v>0.0208</v>
@@ -2671,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-5.8925</v>
+        <v>-6.2161</v>
       </c>
       <c r="E29" t="n">
-        <v>-2.689</v>
+        <v>-2.4967</v>
       </c>
       <c r="F29" t="n">
-        <v>-3.2035</v>
+        <v>-3.7194</v>
       </c>
       <c r="G29" t="n">
         <v>-3.9049</v>
@@ -2716,13 +2716,13 @@
         <v>1.6493</v>
       </c>
       <c r="S29" t="n">
-        <v>0.0857</v>
+        <v>-0.2379</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.9374</v>
+        <v>-0.7451</v>
       </c>
       <c r="U29" t="n">
-        <v>1.023</v>
+        <v>0.5071</v>
       </c>
       <c r="V29" t="n">
         <v>-1.89</v>
@@ -2749,13 +2749,13 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>-13.656</v>
+        <v>-12.3737</v>
       </c>
       <c r="E30" t="n">
         <v>-6.448600000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>-7.2073</v>
+        <v>-5.9251</v>
       </c>
       <c r="G30" t="n">
         <v>-5.0748</v>
@@ -2767,13 +2767,13 @@
         <v>8.815199999999999</v>
       </c>
       <c r="J30" t="n">
-        <v>5.5529</v>
+        <v>5.552900000000002</v>
       </c>
       <c r="K30" t="n">
         <v>-2.6245</v>
       </c>
       <c r="L30" t="n">
-        <v>8.177200000000001</v>
+        <v>8.177199999999999</v>
       </c>
       <c r="M30" t="n">
         <v>-10.6274</v>
@@ -2782,7 +2782,7 @@
         <v>-11.2654</v>
       </c>
       <c r="O30" t="n">
-        <v>0.638</v>
+        <v>0.6379999999999998</v>
       </c>
       <c r="P30" t="n">
         <v>-3.6652</v>
@@ -2794,13 +2794,13 @@
         <v>10.9954</v>
       </c>
       <c r="S30" t="n">
-        <v>-4.947</v>
+        <v>-3.6653</v>
       </c>
       <c r="T30" t="n">
-        <v>-4.049700000000001</v>
+        <v>-4.0497</v>
       </c>
       <c r="U30" t="n">
-        <v>-0.8976000000000004</v>
+        <v>0.3844</v>
       </c>
       <c r="V30" t="n">
         <v>0.03119999999999989</v>
